--- a/public/appartements.xlsx
+++ b/public/appartements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\erp_syndic\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DDC0348-D206-4F6E-9DE7-70DE84B6C094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C07913-E1A2-4722-93C0-70E981EBE666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{8E5B5889-1C32-4F73-A511-5C041FF7D9A4}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="68">
   <si>
     <t>proprietaire_email</t>
   </si>
@@ -54,106 +54,193 @@
     <t>date_signature</t>
   </si>
   <si>
-    <t>Bliving Pavillon D</t>
-  </si>
-  <si>
-    <t>lamia.lahlou@bliving.ma</t>
-  </si>
-  <si>
-    <t>kenza.alaoui.mdaghri@bliving.ma</t>
-  </si>
-  <si>
-    <t>aya.ahmouny@bliving.ma</t>
-  </si>
-  <si>
-    <t>khalil.jabil@bliving.ma</t>
-  </si>
-  <si>
-    <t>bilal.essousi@bliving.ma</t>
-  </si>
-  <si>
-    <t>hicham.elalamy@bliving.ma</t>
-  </si>
-  <si>
-    <t>tawfiq.agoumi@bliving.ma</t>
-  </si>
-  <si>
-    <t>fadwa.chraibi@bliving.ma</t>
-  </si>
-  <si>
-    <t>issam.yaakoubi@bliving.ma</t>
-  </si>
-  <si>
-    <t>yasmine.benabdeslam@bliving.ma</t>
-  </si>
-  <si>
-    <t>abla.chraibi@bliving.ma</t>
-  </si>
-  <si>
-    <t>kamar.habmelouk.sefrioui@bliving.ma</t>
-  </si>
-  <si>
-    <t>salma.mounia.tazi.tazi@bliving.ma</t>
-  </si>
-  <si>
-    <t>soukaina.el.aouissi@bliving.ma</t>
-  </si>
-  <si>
-    <t>zineb.bennouna.louridi@bliving.ma</t>
-  </si>
-  <si>
-    <t>malika.douieb@bliving.ma</t>
-  </si>
-  <si>
-    <t>laila.lahlou@bliving.ma</t>
-  </si>
-  <si>
-    <t>maroua.chetouani@bliving.ma</t>
-  </si>
-  <si>
-    <t>hind.chetouani@bliving.ma</t>
-  </si>
-  <si>
-    <t>mohamed.karim.bensaad@bliving.ma</t>
-  </si>
-  <si>
-    <t>nizar.elasri@bliving.ma</t>
-  </si>
-  <si>
-    <t>salma.ammor@bliving.ma</t>
-  </si>
-  <si>
-    <t>marouane.mzouri@bliving.ma</t>
-  </si>
-  <si>
-    <t>zineb.oukach@bliving.ma</t>
-  </si>
-  <si>
-    <t>youssef.aoulad.touimi@bliving.ma</t>
-  </si>
-  <si>
-    <t>leila.regragui@bliving.ma</t>
-  </si>
-  <si>
-    <t>yuxin.chen.chadia@bliving.ma</t>
-  </si>
-  <si>
-    <t>sarah.benqlilou@bliving.ma</t>
-  </si>
-  <si>
-    <t>ahmed.nabil.lazrak@bliving.ma</t>
-  </si>
-  <si>
-    <t>kenza.bennani.dakhama@bliving.ma</t>
-  </si>
-  <si>
-    <t>maria.tazi@bliving.ma</t>
-  </si>
-  <si>
-    <t>majid.el.guerrab@bliving.ma</t>
-  </si>
-  <si>
-    <t>salwa.ghalim@bliving.ma</t>
+    <t>MAG 1</t>
+  </si>
+  <si>
+    <t>MAG 2</t>
+  </si>
+  <si>
+    <t>MAG 3</t>
+  </si>
+  <si>
+    <t>MAG 4</t>
+  </si>
+  <si>
+    <t>Studio 11</t>
+  </si>
+  <si>
+    <t>Studio 12</t>
+  </si>
+  <si>
+    <t>Studio 13</t>
+  </si>
+  <si>
+    <t>Studio 14</t>
+  </si>
+  <si>
+    <t>Studio 15</t>
+  </si>
+  <si>
+    <t>Studio 16</t>
+  </si>
+  <si>
+    <t>Studio 17</t>
+  </si>
+  <si>
+    <t>Studio 21</t>
+  </si>
+  <si>
+    <t>Studio 22</t>
+  </si>
+  <si>
+    <t>Studio 23</t>
+  </si>
+  <si>
+    <t>Studio 24</t>
+  </si>
+  <si>
+    <t>Studio 25</t>
+  </si>
+  <si>
+    <t>Studio 26</t>
+  </si>
+  <si>
+    <t>Studio 27</t>
+  </si>
+  <si>
+    <t>Studio 31</t>
+  </si>
+  <si>
+    <t>Studio 32</t>
+  </si>
+  <si>
+    <t>Studio 33</t>
+  </si>
+  <si>
+    <t>Studio 34</t>
+  </si>
+  <si>
+    <t>Studio 35</t>
+  </si>
+  <si>
+    <t>Studio 36</t>
+  </si>
+  <si>
+    <t>Studio 37</t>
+  </si>
+  <si>
+    <t>Studio 41</t>
+  </si>
+  <si>
+    <t>Studio 43</t>
+  </si>
+  <si>
+    <t>Studio 44</t>
+  </si>
+  <si>
+    <t>Studio 45</t>
+  </si>
+  <si>
+    <t>Studio 46</t>
+  </si>
+  <si>
+    <t>Studio 47</t>
+  </si>
+  <si>
+    <t>Bliving Bluesky</t>
+  </si>
+  <si>
+    <t>dounia.ettagmouti@bliving.ma</t>
+  </si>
+  <si>
+    <t>jaouad.mernissi@bliving.ma</t>
+  </si>
+  <si>
+    <t>roumane.mohamed.amine@bliving.ma</t>
+  </si>
+  <si>
+    <t>amine.mernissi@bliving.ma</t>
+  </si>
+  <si>
+    <t>yahyaoui.yahyaoui@bliving.ma</t>
+  </si>
+  <si>
+    <t>idrissi.qeytouni.mostafa@bliving.ma</t>
+  </si>
+  <si>
+    <t>hamdaoui.mohamed@bliving.ma</t>
+  </si>
+  <si>
+    <t>atyate.jaafar@bliving.ma</t>
+  </si>
+  <si>
+    <t>mazouz.aziza@bliving.ma</t>
+  </si>
+  <si>
+    <t>berrada.loubna@bliving.ma</t>
+  </si>
+  <si>
+    <t>benjelloun.meryem@bliving.ma</t>
+  </si>
+  <si>
+    <t>albino.jose.martins.jorge@bliving.ma</t>
+  </si>
+  <si>
+    <t>abla.bennani.dakhama@bliving.ma</t>
+  </si>
+  <si>
+    <t>houda.tagmouti@bliving.ma</t>
+  </si>
+  <si>
+    <t>said.ramdi@bliving.ma</t>
+  </si>
+  <si>
+    <t>sahar.messaoudi@bliving.ma</t>
+  </si>
+  <si>
+    <t>ouafae.dardikh@bliving.ma</t>
+  </si>
+  <si>
+    <t>ghislaine.chraibi@bliving.ma</t>
+  </si>
+  <si>
+    <t>zineb.guennnouni@bliving.ma</t>
+  </si>
+  <si>
+    <t>walid.bennani.dakhama@bliving.ma</t>
+  </si>
+  <si>
+    <t>joundy.malik@bliving.ma</t>
+  </si>
+  <si>
+    <t>fikri.mokhtar@bliving.ma</t>
+  </si>
+  <si>
+    <t>charif.karim@bliving.ma</t>
+  </si>
+  <si>
+    <t>zineb.benjelloun@bliving.ma</t>
+  </si>
+  <si>
+    <t>hakimi.fatima.zohra@bliving.ma</t>
+  </si>
+  <si>
+    <t>abdelkrim.chraibi@bliving.ma</t>
+  </si>
+  <si>
+    <t>amor.mamoun@bliving.ma</t>
+  </si>
+  <si>
+    <t>amor.neil@bliving.ma</t>
+  </si>
+  <si>
+    <t>faraj.maryem@bliving.ma</t>
+  </si>
+  <si>
+    <t>chraibi.jorge@bliving.ma</t>
+  </si>
+  <si>
+    <t>imane.kabbaj@bliving.ma</t>
   </si>
 </sst>
 </file>
@@ -205,20 +292,10 @@
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -226,9 +303,21 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -266,13 +355,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor rgb="FFE6B8AF"/>
+        <bgColor rgb="FF00FFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -300,18 +389,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -320,65 +409,32 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="3" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="7" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{8D70224B-5B33-45EB-AB29-1902683E43B3}"/>
     <cellStyle name="Normal 3" xfId="2" xr:uid="{65E6A83A-F5C6-4BB6-9FFE-9B1E4B0034C3}"/>
@@ -693,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{836E5E03-3FAF-4680-960E-72A438E441C7}">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -710,663 +766,577 @@
       <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="8">
-        <v>1</v>
+      <c r="A2" s="8" t="s">
+        <v>5</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="9" t="s">
+      <c r="C2" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="9">
+        <v>45468</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.5">
+      <c r="A3" s="10" t="s">
         <v>6</v>
-      </c>
-      <c r="E2" s="18">
-        <v>45636</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="10">
-        <v>2</v>
       </c>
       <c r="B3" s="1">
         <v>0</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="18">
-        <v>45636</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="11">
-        <v>3</v>
+      <c r="C3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="11">
+        <v>45950</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.5">
+      <c r="A4" s="12" t="s">
+        <v>7</v>
       </c>
       <c r="B4" s="1">
         <v>0</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="19">
-        <v>45742</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="11">
-        <v>4</v>
+      <c r="C4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="13">
+        <v>45095</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.5">
+      <c r="A5" s="10" t="s">
+        <v>8</v>
       </c>
       <c r="B5" s="1">
         <v>0</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="19">
-        <v>45742</v>
+      <c r="C5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="11">
+        <v>45945</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="10">
-        <v>5</v>
+      <c r="A6" s="14" t="s">
+        <v>9</v>
       </c>
       <c r="B6" s="1">
-        <v>0</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="18">
-        <v>45609</v>
+        <v>1</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="15">
+        <v>45905</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="12">
-        <v>101</v>
+      <c r="A7" s="8" t="s">
+        <v>10</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="28">
-        <v>45769</v>
+      <c r="C7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="16">
+        <v>45703</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="11">
-        <v>102</v>
+      <c r="A8" s="14" t="s">
+        <v>11</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="19">
-        <v>45646</v>
+      <c r="C8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="17">
+        <v>45674</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="13">
-        <v>103</v>
+      <c r="A9" s="14" t="s">
+        <v>12</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="20">
-        <v>45658</v>
+      <c r="C9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="17">
+        <v>45670</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="14">
-        <v>104</v>
+      <c r="A10" s="14" t="s">
+        <v>13</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="20">
-        <v>45658</v>
+      <c r="C10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="17">
+        <v>45749</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="13">
-        <v>105</v>
+      <c r="A11" s="14" t="s">
+        <v>14</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="20">
-        <v>45663</v>
+      <c r="C11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="17">
+        <v>45686</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="14">
-        <v>106</v>
+      <c r="A12" s="14" t="s">
+        <v>15</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="21">
-        <v>45742</v>
+      <c r="C12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="17">
+        <v>45685</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="14">
-        <v>107</v>
+      <c r="A13" s="18" t="s">
+        <v>16</v>
       </c>
       <c r="B13" s="1">
-        <v>1</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="21">
-        <v>45604</v>
+        <v>2</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="19">
+        <v>45701</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="14">
-        <v>108</v>
+      <c r="A14" s="14" t="s">
+        <v>17</v>
       </c>
       <c r="B14" s="1">
-        <v>1</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="21">
-        <v>45693</v>
+        <v>2</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="17">
+        <v>45765</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="14">
-        <v>109</v>
+      <c r="A15" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="B15" s="1">
-        <v>1</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="20">
-        <v>45658</v>
+        <v>2</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="17">
+        <v>45713</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="14">
-        <v>201</v>
+      <c r="A16" s="14" t="s">
+        <v>19</v>
       </c>
       <c r="B16" s="1">
         <v>2</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="22">
-        <v>45875</v>
+      <c r="C16" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="17">
+        <v>45678</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="15">
-        <v>202</v>
+      <c r="A17" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="B17" s="1">
         <v>2</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="23">
-        <v>45642</v>
+      <c r="C17" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="16">
+        <v>45812</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="14">
-        <v>203</v>
+      <c r="A18" s="14" t="s">
+        <v>21</v>
       </c>
       <c r="B18" s="1">
         <v>2</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="21">
-        <v>45663</v>
+      <c r="C18" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="17">
+        <v>45679</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="13">
-        <v>204</v>
+      <c r="A19" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="B19" s="1">
         <v>2</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="21">
-        <v>45665</v>
+      <c r="C19" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="20">
+        <v>45895</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="14">
-        <v>205</v>
+      <c r="A20" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="B20" s="1">
-        <v>2</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="21">
-        <v>45663</v>
+        <v>3</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="16">
+        <v>45777</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="14">
-        <v>206</v>
+      <c r="A21" s="14" t="s">
+        <v>24</v>
       </c>
       <c r="B21" s="1">
-        <v>2</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="21">
-        <v>45713</v>
+        <v>3</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="17">
+        <v>45803</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="14">
-        <v>207</v>
+      <c r="A22" s="14" t="s">
+        <v>25</v>
       </c>
       <c r="B22" s="1">
-        <v>2</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="21">
-        <v>45604</v>
+        <v>3</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E22" s="17">
+        <v>45743</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="16">
-        <v>208</v>
+      <c r="A23" s="14" t="s">
+        <v>26</v>
       </c>
       <c r="B23" s="1">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="19">
-        <v>45593</v>
+        <v>3</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E23" s="21">
+        <v>45940</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="14">
-        <v>209</v>
+      <c r="A24" s="14" t="s">
+        <v>27</v>
       </c>
       <c r="B24" s="1">
-        <v>2</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>24</v>
+        <v>3</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="E24" s="20">
-        <v>45593</v>
+        <v>45861</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="14">
-        <v>301</v>
+      <c r="A25" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="B25" s="1">
         <v>3</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="22">
-        <v>45869</v>
+      <c r="C25" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" s="17">
+        <v>45685</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="14">
-        <v>302</v>
+      <c r="A26" s="14" t="s">
+        <v>29</v>
       </c>
       <c r="B26" s="1">
         <v>3</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="21">
-        <v>45643</v>
+      <c r="C26" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E26" s="17">
+        <v>45684</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="12">
-        <v>303</v>
+      <c r="A27" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="B27" s="1">
-        <v>3</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27" s="24">
-        <v>45785</v>
+        <v>4</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" s="17">
+        <v>45702</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="12">
-        <v>304</v>
+      <c r="A28" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="B28" s="1">
-        <v>3</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E28" s="24">
-        <v>45785</v>
+        <v>4</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E28" s="20">
+        <v>45664</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="12">
-        <v>305</v>
+      <c r="A29" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="B29" s="1">
-        <v>3</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E29" s="24">
-        <v>45754</v>
+        <v>4</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29" s="20">
+        <v>45664</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="12">
-        <v>306</v>
+      <c r="A30" s="22" t="s">
+        <v>33</v>
       </c>
       <c r="B30" s="1">
-        <v>3</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E30" s="25">
-        <v>45800</v>
+        <v>4</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E30" s="23">
+        <v>45755</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="14">
-        <v>307</v>
+      <c r="A31" s="14" t="s">
+        <v>34</v>
       </c>
       <c r="B31" s="1">
-        <v>3</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E31" s="21">
-        <v>45706</v>
+        <v>4</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E31" s="17">
+        <v>45667</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="14">
-        <v>308</v>
+      <c r="A32" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="B32" s="1">
-        <v>3</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E32" s="21">
-        <v>45663</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="12">
-        <v>309</v>
-      </c>
-      <c r="B33" s="1">
-        <v>3</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E33" s="24">
-        <v>45588</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="14">
-        <v>401</v>
-      </c>
-      <c r="B34" s="3">
         <v>4</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E34" s="20">
-        <v>45708</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="17">
-        <v>402</v>
-      </c>
-      <c r="B35" s="3">
-        <v>4</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E35" s="26">
-        <v>45693</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="17">
-        <v>403</v>
-      </c>
-      <c r="B36" s="3">
-        <v>4</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E36" s="26">
-        <v>45624</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="17">
-        <v>404</v>
-      </c>
-      <c r="B37" s="3">
-        <v>4</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E37" s="26">
-        <v>45834</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="17">
-        <v>405</v>
-      </c>
-      <c r="B38" s="3">
-        <v>4</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E38" s="27">
-        <v>45646</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="14">
-        <v>406</v>
-      </c>
-      <c r="B39" s="3">
-        <v>4</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E39" s="20">
-        <v>45629</v>
+      <c r="C32" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E32" s="20">
+        <v>45790</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{33DFECCC-41A7-4766-B003-852EF86926E1}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{4E22DE44-9D1E-482F-AA04-8FDAC7D6224F}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{705CCC81-1AD7-4E5E-A9C6-46D375B59CEE}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{6DDE287D-50FB-4E41-8755-67B7E2761B71}"/>
+    <hyperlink ref="D8" r:id="rId5" xr:uid="{6E3B2A55-9150-4BDB-8540-8E42CC0E3103}"/>
+    <hyperlink ref="D9" r:id="rId6" xr:uid="{3AEFE499-4579-4D8C-AD4D-C06C773D61F6}"/>
+    <hyperlink ref="D7" r:id="rId7" xr:uid="{6CB2D315-098F-4B9F-B64F-785F1C66DCC4}"/>
+    <hyperlink ref="D10" r:id="rId8" xr:uid="{4BBFEC55-090B-4840-9E37-A9A1BE57071E}"/>
+    <hyperlink ref="D11" r:id="rId9" xr:uid="{E9EB1FC5-553A-496F-849E-F877F9063703}"/>
+    <hyperlink ref="D12" r:id="rId10" xr:uid="{3059C71E-72DF-407B-BE09-79C89B58EA39}"/>
+    <hyperlink ref="D13" r:id="rId11" xr:uid="{176A8AB6-B60A-45EB-8401-39614EF97C85}"/>
+    <hyperlink ref="D14" r:id="rId12" xr:uid="{25E95F4A-F773-4F14-BD9C-A8087501B941}"/>
+    <hyperlink ref="D15" r:id="rId13" xr:uid="{27F19085-8FDA-4C8A-89B7-0896BE7251F4}"/>
+    <hyperlink ref="D16" r:id="rId14" xr:uid="{12E46677-0497-4357-AD22-60125B2690AD}"/>
+    <hyperlink ref="D17" r:id="rId15" xr:uid="{14E77040-BD29-4DF5-80B8-4C3E0E753F70}"/>
+    <hyperlink ref="D18" r:id="rId16" xr:uid="{E9758631-59D3-4CA4-9EFE-40390F05E96A}"/>
+    <hyperlink ref="D19" r:id="rId17" xr:uid="{78056D48-2419-4201-95E9-BEBBC99FCC0E}"/>
+    <hyperlink ref="D20" r:id="rId18" xr:uid="{682AF41B-388A-4C70-89DD-6C0AE59B285E}"/>
+    <hyperlink ref="D21" r:id="rId19" xr:uid="{ED8B1193-DA13-4F3F-8AB2-91C19569F9F9}"/>
+    <hyperlink ref="D22" r:id="rId20" xr:uid="{0604ED46-8874-450B-947A-892896B4478F}"/>
+    <hyperlink ref="D23" r:id="rId21" xr:uid="{B1B19006-B840-4D53-9681-8C86014E173B}"/>
+    <hyperlink ref="D24" r:id="rId22" xr:uid="{3C98C524-5C9B-41A6-8D72-399F73B6C103}"/>
+    <hyperlink ref="D25" r:id="rId23" xr:uid="{9C311835-47AF-4C1E-9150-99D955BA60A5}"/>
+    <hyperlink ref="D26" r:id="rId24" xr:uid="{43DCF22B-6605-4E60-95A4-2B9823AF934D}"/>
+    <hyperlink ref="D27" r:id="rId25" xr:uid="{F4DE3A31-02DF-46D0-83E3-8AF2CF27B05C}"/>
+    <hyperlink ref="D28" r:id="rId26" xr:uid="{639CF99C-D863-4BB6-9312-243134E6ADF7}"/>
+    <hyperlink ref="D29" r:id="rId27" xr:uid="{4328A26A-F34D-40D9-8A05-D57989B269D2}"/>
+    <hyperlink ref="D30" r:id="rId28" xr:uid="{542E3CB0-B38D-4863-B8CD-BFB4DF3F4F2D}"/>
+    <hyperlink ref="D32" r:id="rId29" xr:uid="{C8270955-7C64-4FED-816E-9328C3034A55}"/>
+    <hyperlink ref="D31" r:id="rId30" xr:uid="{670E7ECA-DE5F-433A-A543-69EA6FC482D5}"/>
+    <hyperlink ref="D6" r:id="rId31" xr:uid="{5FBE1F70-B385-454A-8CE8-C6E7CBD959E8}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>